--- a/output/pdf_financials_xlsx/VNTA.xlsx
+++ b/output/pdf_financials_xlsx/VNTA.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>24.712842</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>24.803229</v>
       </c>
     </row>
     <row r="93">
@@ -2994,7 +2994,11 @@
           <t>Reserve 19,20,21</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>24.712842</v>
       </c>

--- a/output/pdf_financials_xlsx/VNTA.xlsx
+++ b/output/pdf_financials_xlsx/VNTA.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.294791</v>
+        <v>1.791894</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.185846</v>
+        <v>1.730661</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-7.029456</v>
+        <v>-12.042225</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-9.82424</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>2.539014</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.296163</v>
       </c>
     </row>
     <row r="65">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.189189</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.535398</v>
       </c>
     </row>
     <row r="68">
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-7.029456</v>
+        <v>-12.042225</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-9.82424</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.042862</v>
       </c>
     </row>
     <row r="111">
@@ -3154,7 +3154,11 @@
           <t>Net loss from Continuing operations</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-12.042225</v>
       </c>
@@ -3232,7 +3236,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>6.999999999999999e-05</v>
       </c>
@@ -4552,7 +4560,11 @@
           <t>Plant operation and office expenses 5</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>0.497103</v>
       </c>
@@ -5108,7 +5120,11 @@
           <t>Total loss from continuing operations</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
         <v>-12.042225</v>
       </c>
